--- a/population-projection/src/main/resources/population_data/CSK-total-of-50-governorships.xlsx
+++ b/population-projection/src/main/resources/population_data/CSK-total-of-50-governorships.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\population_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7307F17-4CDF-4493-B6A6-86296318E1CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD52EC2-9240-4C04-B976-8D9B28444D20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="4" xr2:uid="{CA9327AE-032E-4159-9FEB-060911109237}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{CA9327AE-032E-4159-9FEB-060911109237}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="рождаемость 1867-1912" sheetId="3" r:id="rId3"/>
     <sheet name="смертность 1867-1912" sheetId="4" r:id="rId4"/>
     <sheet name="естественный прирост 1867-1912" sheetId="5" r:id="rId5"/>
+    <sheet name="младенческая смертность" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>год</t>
   </si>
@@ -64,19 +65,10 @@
     <t>среднее</t>
   </si>
   <si>
-    <t>Поведение рождаемости населения 50 губерний Европейской части России по ЦСК</t>
-  </si>
-  <si>
     <t>минимум обычных колебаний</t>
   </si>
   <si>
     <t>рождаемость</t>
-  </si>
-  <si>
-    <t>Поведение смертности населения 50 губерний Европейской части России по ЦСК</t>
-  </si>
-  <si>
-    <t>Поведение естественного прироста населения 50 губерний Европейской части России по ЦСК</t>
   </si>
   <si>
     <t>смертность</t>
@@ -89,6 +81,75 @@
   </si>
   <si>
     <t>максимум обычных колебаний</t>
+  </si>
+  <si>
+    <t>число
+рождений</t>
+  </si>
+  <si>
+    <t>младенческая смертность:</t>
+  </si>
+  <si>
+    <t>мл. см.</t>
+  </si>
+  <si>
+    <t>число 
+умерших
+в возрасте
+до года</t>
+  </si>
+  <si>
+    <t>участок
+1867-1897</t>
+  </si>
+  <si>
+    <t>участок
+1895-1911</t>
+  </si>
+  <si>
+    <t>C.А. Новосельский, "Обзор главнейших данных по демографии и санитарной статистике России", Пг., 1916, стр. 64-66</t>
+  </si>
+  <si>
+    <t>евреи</t>
+  </si>
+  <si>
+    <t>магометане</t>
+  </si>
+  <si>
+    <t>католики</t>
+  </si>
+  <si>
+    <t>лютеране</t>
+  </si>
+  <si>
+    <t>православные</t>
+  </si>
+  <si>
+    <t>В 1900-1904 гг. младенческая смертность на 1000 родившихся составляла:</t>
+  </si>
+  <si>
+    <t>Младенческая смертность населения 50 губерний Европейской части России по ЦСК</t>
+  </si>
+  <si>
+    <t>Естественный прирост населения 50 губерний Европейской части России по ЦСК</t>
+  </si>
+  <si>
+    <t>Смертность населения 50 губерний Европейской части России по ЦСК</t>
+  </si>
+  <si>
+    <t>Рождаемость населения 50 губерний Европейской части России по ЦСК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокая детская смертность у православнаго, т.е. преимущественно русского населения, стоит, помимо общеизвестных общих причин, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сравнительно низкая смертность у магометан, живущих в общем в весьма антисанитарных условиях, зависит от обязательнаго грудного вскармливания детей, </t>
+  </si>
+  <si>
+    <t>в связи с религиозными предпиcаниями по этому поводу Корана.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в связи с деревенскими обычаями крайне рано, едва ли не с первых дней жизни ребенка, давать ему кроме материнскаго молока жеваный хлеб, кашу и т.п. </t>
   </si>
 </sst>
 </file>
@@ -149,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -170,6 +231,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4127,6 +4194,1450 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>младенческая смертность</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="ru-RU"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>в 50 губерниях европейской</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> части России</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'младенческая смертность'!$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>участок
+1867-1897</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'младенческая смертность'!$A$5:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'младенческая смертность'!$F$5:$F$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>243.15931665704863</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>298.64807450057498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>278.92929518879208</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>248.09796451660341</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>274.0349869118304</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>294.78490943758413</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>262.45580528313525</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>266.18863566058798</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>266.42250064163647</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>277.72548379235775</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>259.96138086027685</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>300.23409222537418</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>252.05788783911055</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>285.92897026542261</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>252.46926606280613</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>300.94668389786131</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>284.26423300191033</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>253.70210222018846</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>270.185075127706</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>248.0962405076323</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>255.80551005930673</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>250.06483388819893</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>274.83374785621146</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>291.80553535253188</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>272.08462866893592</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>306.69196871524332</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>252.0020017108998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>264.90906168012174</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>279.82633852487766</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>274.00050358062225</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>259.51318037403831</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9199-46C8-B057-AEBFF533C6C3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'младенческая смертность'!$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>участок
+1895-1911</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="92D050"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="00B050"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'младенческая смертность'!$A$5:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'младенческая смертность'!$G$5:$G$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="28" formatCode="0.0">
+                  <c:v>279.82633852487766</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="0.0">
+                  <c:v>274.00050358062225</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="0.0">
+                  <c:v>259.51318037403831</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="0.0">
+                  <c:v>278.82430617019611</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="0.0">
+                  <c:v>239.6818840643586</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="0.0">
+                  <c:v>252.42737448813341</c:v>
+                </c:pt>
+                <c:pt idx="34" formatCode="0.0">
+                  <c:v>271.61432894761504</c:v>
+                </c:pt>
+                <c:pt idx="35" formatCode="0.0">
+                  <c:v>258.19686905196778</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="0.0">
+                  <c:v>256.25569345389647</c:v>
+                </c:pt>
+                <c:pt idx="37" formatCode="0.0">
+                  <c:v>231.62743846086599</c:v>
+                </c:pt>
+                <c:pt idx="38" formatCode="0.0">
+                  <c:v>271.50964380326326</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="0.0">
+                  <c:v>247.95790811519026</c:v>
+                </c:pt>
+                <c:pt idx="40" formatCode="0.0">
+                  <c:v>225.44897409270067</c:v>
+                </c:pt>
+                <c:pt idx="41" formatCode="0.0">
+                  <c:v>244.11617976544531</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="0.0">
+                  <c:v>248.01735995640885</c:v>
+                </c:pt>
+                <c:pt idx="43" formatCode="0.0">
+                  <c:v>273.88834095696774</c:v>
+                </c:pt>
+                <c:pt idx="44" formatCode="0.0">
+                  <c:v>237.32069579314185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9199-46C8-B057-AEBFF533C6C3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="780498944"/>
+        <c:axId val="780499600"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'младенческая смертность'!$D$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>мл. см.</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'младенческая смертность'!$A$5:$A$49</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="45"/>
+                      <c:pt idx="0">
+                        <c:v>1867</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1868</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1869</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1870</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1871</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1872</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1873</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1874</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1875</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1876</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1877</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1878</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1880</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1881</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1882</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1883</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1884</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1885</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1886</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1887</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1888</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1889</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1890</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1891</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1892</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1893</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1894</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1895</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1896</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1898</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1899</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1900</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1901</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>1902</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>1903</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>1904</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>1905</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>1906</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>1907</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>1909</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>1910</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>1911</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'младенческая смертность'!$D$5:$D$49</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.0</c:formatCode>
+                      <c:ptCount val="45"/>
+                      <c:pt idx="0">
+                        <c:v>243.15931665704863</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>298.64807450057498</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>278.92929518879208</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>248.09796451660341</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>274.0349869118304</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>294.78490943758413</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>262.45580528313525</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>266.18863566058798</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>266.42250064163647</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>277.72548379235775</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>259.96138086027685</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>300.23409222537418</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>252.05788783911055</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>285.92897026542261</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>252.46926606280613</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>300.94668389786131</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>284.26423300191033</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>253.70210222018846</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>270.185075127706</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>248.0962405076323</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>255.80551005930673</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>250.06483388819893</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>274.83374785621146</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>291.80553535253188</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>272.08462866893592</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>306.69196871524332</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>252.0020017108998</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>264.90906168012174</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>279.82633852487766</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>274.00050358062225</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>259.51318037403831</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>278.82430617019611</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>239.6818840643586</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>252.42737448813341</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>271.61432894761504</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>258.19686905196778</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>256.25569345389647</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>231.62743846086599</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>271.50964380326326</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>247.95790811519026</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>225.44897409270067</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>244.11617976544531</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>248.01735995640885</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>273.88834095696774</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>237.32069579314185</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-9199-46C8-B057-AEBFF533C6C3}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'младенческая смертность'!$E$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'младенческая смертность'!$A$5:$A$49</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="45"/>
+                      <c:pt idx="0">
+                        <c:v>1867</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1868</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1869</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1870</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1871</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1872</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1873</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1874</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1875</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1876</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1877</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1878</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1880</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1881</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1882</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1883</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1884</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1885</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1886</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1887</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1888</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1889</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1890</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1891</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1892</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1893</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1894</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1895</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1896</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>1898</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>1899</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>1900</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>1901</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>1902</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>1903</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>1904</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>1905</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>1906</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>1907</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="42">
+                        <c:v>1909</c:v>
+                      </c:pt>
+                      <c:pt idx="43">
+                        <c:v>1910</c:v>
+                      </c:pt>
+                      <c:pt idx="44">
+                        <c:v>1911</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'младенческая смертность'!$E$5:$E$49</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="45"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-9199-46C8-B057-AEBFF533C6C3}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="780498944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="1865"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="780499600"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="5"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="780499600"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="310"/>
+          <c:min val="220"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="780498944"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1800" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4208,6 +5719,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5795,6 +7346,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -5898,6 +7965,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DCC1997-F1D0-4793-AE56-F45B04267F89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>166686</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7327217A-607C-4B7C-8C7C-8189FB1C50BB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6252,11 +8360,17 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -6479,7 +8593,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -7295,7 +9409,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -7303,13 +9417,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8106,7 +10220,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -8114,13 +10228,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -8921,7 +11035,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -8935,13 +11049,13 @@
         <v>3</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10051,4 +12165,1068 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416C74C9-3CCB-48C3-8549-9DE3B52F6A04}">
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1867</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3101810</v>
+      </c>
+      <c r="C5" s="2">
+        <v>754234</v>
+      </c>
+      <c r="D5" s="1">
+        <f>C5/B5*1000</f>
+        <v>243.15931665704863</v>
+      </c>
+      <c r="F5" s="1">
+        <f>D5</f>
+        <v>243.15931665704863</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f>A5+1</f>
+        <v>1868</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2951494</v>
+      </c>
+      <c r="C6" s="2">
+        <v>881458</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" ref="D6:D49" si="0">C6/B6*1000</f>
+        <v>298.64807450057498</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" ref="F6:F37" si="1">D6</f>
+        <v>298.64807450057498</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" ref="A7:A50" si="2">A6+1</f>
+        <v>1869</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3004152</v>
+      </c>
+      <c r="C7" s="2">
+        <v>837946</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>278.92929518879208</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="1"/>
+        <v>278.92929518879208</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="2"/>
+        <v>1870</v>
+      </c>
+      <c r="B8" s="2">
+        <v>3134931</v>
+      </c>
+      <c r="C8" s="2">
+        <v>777770</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>248.09796451660341</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="1"/>
+        <v>248.09796451660341</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="2"/>
+        <v>1871</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3132600</v>
+      </c>
+      <c r="C9" s="2">
+        <v>858442</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>274.0349869118304</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="1"/>
+        <v>274.0349869118304</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="2"/>
+        <v>1872</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3109016</v>
+      </c>
+      <c r="C10" s="2">
+        <v>916491</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>294.78490943758413</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="1"/>
+        <v>294.78490943758413</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="2"/>
+        <v>1873</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3321664</v>
+      </c>
+      <c r="C11" s="2">
+        <v>871790</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>262.45580528313525</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="1"/>
+        <v>262.45580528313525</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="2"/>
+        <v>1874</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3326423</v>
+      </c>
+      <c r="C12" s="2">
+        <v>885456</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>266.18863566058798</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="1"/>
+        <v>266.18863566058798</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="2"/>
+        <v>1875</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3389770</v>
+      </c>
+      <c r="C13" s="2">
+        <v>903111</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>266.42250064163647</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="1"/>
+        <v>266.42250064163647</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="2"/>
+        <v>1876</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3196671</v>
+      </c>
+      <c r="C14" s="2">
+        <v>887797</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>277.72548379235775</v>
+      </c>
+      <c r="F14" s="1">
+        <f t="shared" si="1"/>
+        <v>277.72548379235775</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="2"/>
+        <v>1877</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3096910</v>
+      </c>
+      <c r="C15" s="2">
+        <v>805077</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>259.96138086027685</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="1"/>
+        <v>259.96138086027685</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="2"/>
+        <v>1878</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2843751</v>
+      </c>
+      <c r="C16" s="2">
+        <v>853791</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>300.23409222537418</v>
+      </c>
+      <c r="F16" s="1">
+        <f t="shared" si="1"/>
+        <v>300.23409222537418</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="2"/>
+        <v>1879</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3123834</v>
+      </c>
+      <c r="C17" s="2">
+        <v>787387</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>252.05788783911055</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="1"/>
+        <v>252.05788783911055</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="2"/>
+        <v>1880</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3352427</v>
+      </c>
+      <c r="C18" s="2">
+        <v>958556</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>285.92897026542261</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="1"/>
+        <v>285.92897026542261</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="2"/>
+        <v>1881</v>
+      </c>
+      <c r="B19" s="2">
+        <v>3369321</v>
+      </c>
+      <c r="C19" s="2">
+        <v>850650</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>252.46926606280613</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="1"/>
+        <v>252.46926606280613</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="2"/>
+        <v>1882</v>
+      </c>
+      <c r="B20" s="2">
+        <v>3876690</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1166677</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>300.94668389786131</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="1"/>
+        <v>300.94668389786131</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="2"/>
+        <v>1883</v>
+      </c>
+      <c r="B21" s="2">
+        <v>3784690</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1075852</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
+        <v>284.26423300191033</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="1"/>
+        <v>284.26423300191033</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="2"/>
+        <v>1884</v>
+      </c>
+      <c r="B22" s="2">
+        <v>4007858</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1016802</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>253.70210222018846</v>
+      </c>
+      <c r="F22" s="1">
+        <f t="shared" si="1"/>
+        <v>253.70210222018846</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="2"/>
+        <v>1885</v>
+      </c>
+      <c r="B23" s="2">
+        <v>3957528</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1069265</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="0"/>
+        <v>270.185075127706</v>
+      </c>
+      <c r="F23" s="1">
+        <f t="shared" si="1"/>
+        <v>270.185075127706</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="2"/>
+        <v>1886</v>
+      </c>
+      <c r="B24" s="2">
+        <v>3972797</v>
+      </c>
+      <c r="C24" s="2">
+        <v>985636</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="0"/>
+        <v>248.0962405076323</v>
+      </c>
+      <c r="F24" s="1">
+        <f t="shared" si="1"/>
+        <v>248.0962405076323</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="2"/>
+        <v>1887</v>
+      </c>
+      <c r="B25" s="2">
+        <v>4062606</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1039237</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="0"/>
+        <v>255.80551005930673</v>
+      </c>
+      <c r="F25" s="1">
+        <f t="shared" si="1"/>
+        <v>255.80551005930673</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="2"/>
+        <v>1888</v>
+      </c>
+      <c r="B26" s="2">
+        <v>4268601</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1067427</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="0"/>
+        <v>250.06483388819893</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" si="1"/>
+        <v>250.06483388819893</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="2"/>
+        <v>1889</v>
+      </c>
+      <c r="B27" s="2">
+        <v>4232577</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1163255</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="0"/>
+        <v>274.83374785621146</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="1"/>
+        <v>274.83374785621146</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="2"/>
+        <v>1890</v>
+      </c>
+      <c r="B28" s="2">
+        <v>4227915</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1233729</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="0"/>
+        <v>291.80553535253188</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="1"/>
+        <v>291.80553535253188</v>
+      </c>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="2"/>
+        <v>1891</v>
+      </c>
+      <c r="B29" s="2">
+        <v>4372419</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1189668</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>272.08462866893592</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="1"/>
+        <v>272.08462866893592</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="2"/>
+        <v>1892</v>
+      </c>
+      <c r="B30" s="2">
+        <v>4033402</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1237012</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="0"/>
+        <v>306.69196871524332</v>
+      </c>
+      <c r="F30" s="1">
+        <f t="shared" si="1"/>
+        <v>306.69196871524332</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="2"/>
+        <v>1893</v>
+      </c>
+      <c r="B31" s="2">
+        <v>4298323</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1083186</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="0"/>
+        <v>252.0020017108998</v>
+      </c>
+      <c r="F31" s="1">
+        <f t="shared" si="1"/>
+        <v>252.0020017108998</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="2"/>
+        <v>1894</v>
+      </c>
+      <c r="B32" s="2">
+        <v>4391658</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1163390</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="0"/>
+        <v>264.90906168012174</v>
+      </c>
+      <c r="F32" s="1">
+        <f t="shared" si="1"/>
+        <v>264.90906168012174</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="2"/>
+        <v>1895</v>
+      </c>
+      <c r="B33" s="2">
+        <v>4539176</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1270181</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="0"/>
+        <v>279.82633852487766</v>
+      </c>
+      <c r="F33" s="1">
+        <f t="shared" si="1"/>
+        <v>279.82633852487766</v>
+      </c>
+      <c r="G33" s="1">
+        <f>D33</f>
+        <v>279.82633852487766</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="2"/>
+        <v>1896</v>
+      </c>
+      <c r="B34" s="2">
+        <v>4634809</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1269940</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="0"/>
+        <v>274.00050358062225</v>
+      </c>
+      <c r="F34" s="1">
+        <f>D34</f>
+        <v>274.00050358062225</v>
+      </c>
+      <c r="G34" s="1">
+        <f t="shared" ref="G34:G49" si="3">D34</f>
+        <v>274.00050358062225</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="2"/>
+        <v>1897</v>
+      </c>
+      <c r="B35" s="2">
+        <v>4692621</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1217797</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="0"/>
+        <v>259.51318037403831</v>
+      </c>
+      <c r="F35" s="1">
+        <f>D35</f>
+        <v>259.51318037403831</v>
+      </c>
+      <c r="G35" s="1">
+        <f t="shared" si="3"/>
+        <v>259.51318037403831</v>
+      </c>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="2"/>
+        <v>1898</v>
+      </c>
+      <c r="B36" s="2">
+        <v>4625558</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1289718</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="0"/>
+        <v>278.82430617019611</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <f t="shared" si="3"/>
+        <v>278.82430617019611</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="2"/>
+        <v>1899</v>
+      </c>
+      <c r="B37" s="2">
+        <v>4764678</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1142007</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="0"/>
+        <v>239.6818840643586</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <f t="shared" si="3"/>
+        <v>239.6818840643586</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="2"/>
+        <v>1900</v>
+      </c>
+      <c r="B38" s="2">
+        <v>4853804</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1225233</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="0"/>
+        <v>252.42737448813341</v>
+      </c>
+      <c r="G38" s="1">
+        <f t="shared" si="3"/>
+        <v>252.42737448813341</v>
+      </c>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="2"/>
+        <v>1901</v>
+      </c>
+      <c r="B39" s="2">
+        <v>4801190</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1304072</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="0"/>
+        <v>271.61432894761504</v>
+      </c>
+      <c r="G39" s="1">
+        <f t="shared" si="3"/>
+        <v>271.61432894761504</v>
+      </c>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="2"/>
+        <v>1902</v>
+      </c>
+      <c r="B40" s="2">
+        <v>4993248</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1289241</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="0"/>
+        <v>258.19686905196778</v>
+      </c>
+      <c r="G40" s="1">
+        <f t="shared" si="3"/>
+        <v>258.19686905196778</v>
+      </c>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="2"/>
+        <v>1903</v>
+      </c>
+      <c r="B41" s="2">
+        <v>4978305</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1275719</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="0"/>
+        <v>256.25569345389647</v>
+      </c>
+      <c r="G41" s="1">
+        <f t="shared" si="3"/>
+        <v>256.25569345389647</v>
+      </c>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="2"/>
+        <v>1904</v>
+      </c>
+      <c r="B42" s="2">
+        <v>5124544</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1186985</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="0"/>
+        <v>231.62743846086599</v>
+      </c>
+      <c r="G42" s="1">
+        <f t="shared" si="3"/>
+        <v>231.62743846086599</v>
+      </c>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="2"/>
+        <v>1905</v>
+      </c>
+      <c r="B43" s="2">
+        <v>4830252</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1311460</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="0"/>
+        <v>271.50964380326326</v>
+      </c>
+      <c r="G43" s="1">
+        <f t="shared" si="3"/>
+        <v>271.50964380326326</v>
+      </c>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="2"/>
+        <v>1906</v>
+      </c>
+      <c r="B44" s="2">
+        <v>5120607</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1269695</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="0"/>
+        <v>247.95790811519026</v>
+      </c>
+      <c r="G44" s="1">
+        <f t="shared" si="3"/>
+        <v>247.95790811519026</v>
+      </c>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="2"/>
+        <v>1907</v>
+      </c>
+      <c r="B45" s="2">
+        <v>5258711</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1185571</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="0"/>
+        <v>225.44897409270067</v>
+      </c>
+      <c r="G45" s="1">
+        <f t="shared" si="3"/>
+        <v>225.44897409270067</v>
+      </c>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="2"/>
+        <v>1908</v>
+      </c>
+      <c r="B46" s="2">
+        <v>5049313</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1232619</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="0"/>
+        <v>244.11617976544531</v>
+      </c>
+      <c r="G46" s="1">
+        <f t="shared" si="3"/>
+        <v>244.11617976544531</v>
+      </c>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="2"/>
+        <v>1909</v>
+      </c>
+      <c r="B47" s="2">
+        <v>5123976</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1270835</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="0"/>
+        <v>248.01735995640885</v>
+      </c>
+      <c r="G47" s="1">
+        <f t="shared" si="3"/>
+        <v>248.01735995640885</v>
+      </c>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="2"/>
+        <v>1910</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3409791</v>
+      </c>
+      <c r="C48" s="2">
+        <v>933902</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="0"/>
+        <v>273.88834095696774</v>
+      </c>
+      <c r="G48" s="1">
+        <f t="shared" si="3"/>
+        <v>273.88834095696774</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="2"/>
+        <v>1911</v>
+      </c>
+      <c r="B49" s="2">
+        <v>3587618</v>
+      </c>
+      <c r="C49" s="2">
+        <v>851416</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="0"/>
+        <v>237.32069579314185</v>
+      </c>
+      <c r="G49" s="1">
+        <f t="shared" si="3"/>
+        <v>237.32069579314185</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>